--- a/output/pdf_financials_xlsx/SHOW.xlsx
+++ b/output/pdf_financials_xlsx/SHOW.xlsx
@@ -1941,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.194028</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.194028</v>
       </c>
     </row>
     <row r="93">
@@ -3083,7 +3083,11 @@
           <t>Reserves (Note 9) (Note 15)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SHOW.xlsx
+++ b/output/pdf_financials_xlsx/SHOW.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.101352</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.060895</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.003648</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.101352</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.060895</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.003648</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.849139</v>
+        <v>0.747787</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.08967899999999999</v>
+        <v>0.028784</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.032432</v>
+        <v>0.028784</v>
       </c>
     </row>
     <row r="49">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -2765,7 +2765,11 @@
           <t>Reclamation deposit (Note 5)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
